--- a/employee_surveys/018_safety_perception_survey--employee_surveys.xlsx
+++ b/employee_surveys/018_safety_perception_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>page1_label</t>
+          <t>page1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>page2_label</t>
+          <t>page2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>page3</t>
+          <t>safety_perception</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>page3_label</t>
+          <t>How safe do you feel when walking alone at night?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>safety_perception</t>
+          <t>page2_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How safe do you feel when walking alone at night?</t>
+          <t>Page2 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page2</t>
+          <t>safety_perception_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>page2_label</t>
+          <t>Do you feel safe when walking alone on campus?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>safety_perception_2</t>
+          <t>page3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Do you feel safe when walking alone on campus?</t>
+          <t>page3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>page2</t>
+          <t>safety_perception_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>page2_label</t>
+          <t>How safe do you feel when you're walking on a parking lot or garage?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>safety_perception_3</t>
+          <t>page4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How safe do you feel when you're walking on a parking lot or garage?</t>
+          <t>page4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>page3</t>
+          <t>safety_perception_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>page3_label</t>
+          <t>Do you feel safe when you are walking in a poorly lit area?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>safety_perception_4</t>
+          <t>page5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Do you feel safe when you are walking in a poorly lit area?</t>
+          <t>page5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>page3</t>
+          <t>safety_perception_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>page3_label</t>
+          <t>Do you feel safe when you are alone in a parking garage?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>safety_perception_5</t>
+          <t>page6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Do you feel safe when you are alone in a parking garage?</t>
+          <t>page6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>page3</t>
+          <t>safety_score</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>page3_label</t>
+          <t>How would you rate your sense of safety on a scale of 1 to 5?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>safety_score</t>
+          <t>page7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How would you rate your sense of safety on a scale of 1 to 5?</t>
+          <t>page7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>page4</t>
+          <t>safety_score_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>page4_label</t>
+          <t>Would you rate your sense of safety as 1-5 when walking in a poorly lit area?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>safety_score_2</t>
+          <t>page8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Would you rate your sense of safety as 1?</t>
+          <t>page8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>page4</t>
+          <t>safety_score_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>page4_label</t>
+          <t>How would you rate your sense of safety when walking alone in a parking garage?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>safety_score_3</t>
+          <t>page9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How would you rate your sense of safety when walking alone in a parking garage?</t>
+          <t>page9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>page4</t>
+          <t>safety_perception_6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>page4_label</t>
+          <t>Are there any areas around the parking garage that are considered unsafe?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,17 +952,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>safety_score_4</t>
+          <t>page10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Would you rate your sense of safety as 1-5 when walking in a poorly lit area?</t>
+          <t>page10</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,62 +980,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>page5</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>page5_label</t>
+          <t>Any additional comments?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>page5</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>page5_label</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>safety_perception_6</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Are there any areas around the parking garage that are considered unsafe?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1052,7 +1006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1544,12 +1498,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_safe</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very safe</t>
         </is>
       </c>
     </row>
@@ -1561,46 +1515,46 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_safe</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Somewhat safe</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>safety_score_3_choices</t>
+          <t>safety_score_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>strongly_agree</t>
+          <t>not_very_safe</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Strongly agree</t>
+          <t>Not very safe</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>safety_score_3_choices</t>
+          <t>safety_score_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>somewhat_agree</t>
+          <t>not_at_all_safe</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Somewhat agree</t>
+          <t>Not at all safe</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1566,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
@@ -1629,12 +1583,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>somewhat_disagree</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Somewhat disagree</t>
+          <t>Somewhat agree</t>
         </is>
       </c>
     </row>
@@ -1646,114 +1600,80 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>strongly_disagree</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Strongly disagree</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>safety_score_4_choices</t>
+          <t>safety_score_3_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>very_safe</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Very safe</t>
+          <t>Somewhat disagree</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>safety_score_4_choices</t>
+          <t>safety_score_3_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>somewhat_safe</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Somewhat safe</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>safety_score_4_choices</t>
+          <t>safety_perception_6_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>not_very_safe</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Not very safe</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>safety_score_4_choices</t>
+          <t>safety_perception_6_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>not_at_all_safe</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Not at all safe</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>safety_perception_6_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>safety_perception_6_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
